--- a/check_in_forms/049_golf_course_player_check_in--check_in_forms.xlsx
+++ b/check_in_forms/049_golf_course_player_check_in--check_in_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{7:_'am'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{7: 'AM'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{12:_'pm'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{12: 'PM'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{1:_9}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{1: 9}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{2:_10}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{2: 10}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{3:_11}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{3: 11}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{4:_12}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{4: 12}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{5:_1}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{5: 1}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{6:_2}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{6: 2}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{1:_'1-4_players'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{1: '1-4 players'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{2:_'5-6_players'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{2: '5-6 players'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{3:_'7-10_players'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{3: '7-10 players'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{4:_'11_players_or_more'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{4: '11 players or more'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{1:_'1_player'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{1: '1 player'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{2:_'2_players'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{2: '2 players'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{3:_'3_players'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{3: '3 players'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{4:_'4_players'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{4: '4 players'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{5:_'5_players'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{5: '5 players'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{6:_'6_players'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{6: '6 players'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{7:_'7_players'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{7: '7 players'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{8:_'8_players'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{8: '8 players'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{9:_'9_players'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{9: '9 players'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{10:_'10_players'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{10: '10 players'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{11:_'11_players'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{11: '11 players'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{12:_'12_players'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{12: '12 players'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{13:_'13_players'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{13: '13 players'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{14:_'14_players'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{14: '14 players'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{15:_'15_players'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{15: '15 players'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{16:_'16_players'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{16: '16 players'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{17:_'17_players'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{17: '17 players'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{18:_'18_players'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{18: '18 players'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{19:_'19_players'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{19: '19 players'}</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{20:_'20_players'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{20: '20 players'}</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{21:_'21_players'}</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{21: '21 players'}</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{22:_'22_players'}</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{22: '22 players'}</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{23:_'23_players'}</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{23: '23 players'}</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{24:_'24_players'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{24: '24 players'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{25:_'25_players'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{25: '25 players'}</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{26:_'26_players'}</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{26: '26 players'}</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{27:_'27_players'}</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{27: '27 players'}</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{28:_'28_players'}</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{28: '28 players'}</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{29:_'29_players'}</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{29: '29 players'}</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{30:_'30_players'}</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{30: '30 players'}</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{31:_'31_players'}</t>
+          <t>option_31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{31: '31 players'}</t>
+          <t>Option 31</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{32:_'32_players'}</t>
+          <t>option_32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{32: '32 players'}</t>
+          <t>Option 32</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{33:_'33_players'}</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{33: '33 players'}</t>
+          <t>Option 33</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{34:_'34_players'}</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{34: '34 players'}</t>
+          <t>Option 34</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{35:_'35_players'}</t>
+          <t>option_35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{35: '35 players'}</t>
+          <t>Option 35</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{36:_'36_players'}</t>
+          <t>option_36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{36: '36 players'}</t>
+          <t>Option 36</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{37:_'37_players'}</t>
+          <t>option_37</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{37: '37 players'}</t>
+          <t>Option 37</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{38:_'38_players'}</t>
+          <t>option_38</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{38: '38 players'}</t>
+          <t>Option 38</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{39:_'39_players'}</t>
+          <t>option_39</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{39: '39 players'}</t>
+          <t>Option 39</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{40:_'40_players'}</t>
+          <t>option_40</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{40: '40 players'}</t>
+          <t>Option 40</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{41:_'41_players'}</t>
+          <t>option_41</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{41: '41 players'}</t>
+          <t>Option 41</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{42:_'42_players'}</t>
+          <t>option_42</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{42: '42 players'}</t>
+          <t>Option 42</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{43:_'43_players'}</t>
+          <t>option_43</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{43: '43 players'}</t>
+          <t>Option 43</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{44:_'44_players'}</t>
+          <t>option_44</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{44: '44 players'}</t>
+          <t>Option 44</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{45:_'45_players'}</t>
+          <t>option_45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{45: '45 players'}</t>
+          <t>Option 45</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{46:_'46_players'}</t>
+          <t>option_46</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{46: '46 players'}</t>
+          <t>Option 46</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{47:_'47_players'}</t>
+          <t>option_47</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{47: '47 players'}</t>
+          <t>Option 47</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{48:_'48_players'}</t>
+          <t>option_48</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{48: '48 players'}</t>
+          <t>Option 48</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{49:_'49_players'}</t>
+          <t>option_49</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{49: '49 players'}</t>
+          <t>Option 49</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{50:_'50_players'}</t>
+          <t>option_50</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{50: '50 players'}</t>
+          <t>Option 50</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{1:_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{1: True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{2:_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{2: False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
